--- a/rules/CORE-000765/negative/01/data/unit-test-coreid-FB2401-negative_01.xlsx
+++ b/rules/CORE-000765/negative/01/data/unit-test-coreid-FB2401-negative_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000765\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3C1150-B089-4D1A-BF5E-6C31E682AAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFDE86F-A651-4685-8DB4-407BB82D140D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
   <si>
     <t>Product</t>
   </si>
@@ -253,6 +253,15 @@
   </si>
   <si>
     <t>File Size</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>$dataset_size</t>
   </si>
 </sst>
 </file>
@@ -339,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -361,9 +370,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -711,7 +717,7 @@
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
@@ -733,8 +739,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -754,6 +764,26 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2">
+        <v>5368709121</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +1010,7 @@
       <c r="M5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1022,7 +1052,7 @@
       <c r="M6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1062,7 +1092,7 @@
       <c r="M7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="10" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1106,7 +1136,7 @@
       <c r="M8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="10" t="s">
         <v>74</v>
       </c>
     </row>
